--- a/health_tracking_forms/027_weekly_body_measurements_tracking_form--health_tracking_forms.xlsx
+++ b/health_tracking_forms/027_weekly_body_measurements_tracking_form--health_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'chest'}</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Chest'}</t>
+          <t>Chest</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hips'}</t>
+          <t>hips</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hips'}</t>
+          <t>Hips</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'waist'}</t>
+          <t>waist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Waist'}</t>
+          <t>Waist</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'shoulders'}</t>
+          <t>shoulders</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Shoulders'}</t>
+          <t>Shoulders</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'hips_circumference'}</t>
+          <t>hips_circumference</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Hips Circumference'}</t>
+          <t>Hips Circumference</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'waist_circumference'}</t>
+          <t>waist_circumference</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Waist Circumference'}</t>
+          <t>Waist Circumference</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'neck'}</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Neck'}</t>
+          <t>Neck</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'hip_circumference'}</t>
+          <t>hip_circumference</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Hip Circumference'}</t>
+          <t>Hip Circumference</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'thigh'}</t>
+          <t>thigh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Thigh'}</t>
+          <t>Thigh</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'shoulder_circumference'}</t>
+          <t>shoulder_circumference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Shoulder Circumference'}</t>
+          <t>Shoulder Circumference</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'arm'}</t>
+          <t>arm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Arm'}</t>
+          <t>Arm</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'calf'}</t>
+          <t>calf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Calf'}</t>
+          <t>Calf</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'thigh_circumference'}</t>
+          <t>thigh_circumference</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Thigh Circumference'}</t>
+          <t>Thigh Circumference</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'forearm'}</t>
+          <t>forearm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Forearm'}</t>
+          <t>Forearm</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'calf_circumference'}</t>
+          <t>calf_circumference</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Calf Circumference'}</t>
+          <t>Calf Circumference</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'forearm_circumference'}</t>
+          <t>forearm_circumference</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Forearm Circumference'}</t>
+          <t>Forearm Circumference</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'send_report'}</t>
+          <t>send_report</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Send Report'}</t>
+          <t>Send Report</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'no_action'}</t>
+          <t>no_action</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'No Action'}</t>
+          <t>No Action</t>
         </is>
       </c>
     </row>
